--- a/task464/golden/area_capacity_2027.xlsx
+++ b/task464/golden/area_capacity_2027.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -642,7 +641,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ammerly</t>
+          <t>Granleigh</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -666,7 +665,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bexhollow</t>
+          <t>Lowenbrook</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -692,7 +691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crannock</t>
+          <t>Ammerly</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -716,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -742,7 +741,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eastmoor Reach</t>
+          <t>Crannock</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -766,7 +765,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fallowbray</t>
+          <t>Innsmere</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -790,7 +789,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Granleigh</t>
+          <t>Bexhollow</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -816,7 +815,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hesper Vale</t>
+          <t>Kettlebrook</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -840,7 +839,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Innsmere</t>
+          <t>Eastmoor Reach</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -866,7 +865,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jarrowmead</t>
+          <t>Durnsfield</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -890,7 +889,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kettlebrook</t>
+          <t>Jarrowmead</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -916,7 +915,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lowenbrook</t>
+          <t>Fallowbray</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -961,7 +960,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -1050,7 +1049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ammerly</t>
+          <t>Granleigh</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -1073,7 +1072,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ammerly</t>
+          <t>Granleigh</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1096,7 +1095,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bexhollow</t>
+          <t>Lowenbrook</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -1119,7 +1118,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bexhollow</t>
+          <t>Lowenbrook</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1142,7 +1141,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crannock</t>
+          <t>Ammerly</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1165,7 +1164,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crannock</t>
+          <t>Ammerly</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1188,7 +1187,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1234,7 +1233,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eastmoor Reach</t>
+          <t>Crannock</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1257,7 +1256,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eastmoor Reach</t>
+          <t>Crannock</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1280,7 +1279,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fallowbray</t>
+          <t>Innsmere</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1303,7 +1302,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fallowbray</t>
+          <t>Innsmere</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1326,7 +1325,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Granleigh</t>
+          <t>Bexhollow</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1349,7 +1348,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Granleigh</t>
+          <t>Bexhollow</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1372,7 +1371,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hesper Vale</t>
+          <t>Kettlebrook</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1395,7 +1394,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hesper Vale</t>
+          <t>Kettlebrook</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1418,7 +1417,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Innsmere</t>
+          <t>Eastmoor Reach</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1441,7 +1440,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Innsmere</t>
+          <t>Eastmoor Reach</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1464,7 +1463,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jarrowmead</t>
+          <t>Durnsfield</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -1487,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jarrowmead</t>
+          <t>Durnsfield</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1510,7 +1509,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kettlebrook</t>
+          <t>Jarrowmead</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1533,7 +1532,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kettlebrook</t>
+          <t>Jarrowmead</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1556,7 +1555,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lowenbrook</t>
+          <t>Fallowbray</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1579,7 +1578,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lowenbrook</t>
+          <t>Fallowbray</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1644,7 +1643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ammerly</t>
+          <t>Granleigh</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
@@ -1662,7 +1661,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bexhollow</t>
+          <t>Lowenbrook</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
@@ -1680,7 +1679,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crannock</t>
+          <t>Ammerly</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
@@ -1698,7 +1697,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
@@ -1716,7 +1715,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eastmoor Reach</t>
+          <t>Crannock</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
@@ -1734,7 +1733,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fallowbray</t>
+          <t>Innsmere</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
@@ -1752,7 +1751,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Granleigh</t>
+          <t>Bexhollow</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
@@ -1770,7 +1769,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hesper Vale</t>
+          <t>Kettlebrook</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -1788,7 +1787,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Innsmere</t>
+          <t>Eastmoor Reach</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -1806,7 +1805,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jarrowmead</t>
+          <t>Durnsfield</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -1824,7 +1823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kettlebrook</t>
+          <t>Jarrowmead</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
@@ -1842,7 +1841,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lowenbrook</t>
+          <t>Fallowbray</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
@@ -1902,7 +1901,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ammerly</t>
+          <t>Granleigh</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
@@ -1920,7 +1919,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bexhollow</t>
+          <t>Lowenbrook</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
@@ -1938,7 +1937,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crannock</t>
+          <t>Ammerly</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
@@ -1956,7 +1955,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Durnsfield</t>
+          <t>Hesper Vale</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
@@ -1974,7 +1973,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eastmoor Reach</t>
+          <t>Crannock</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
@@ -1992,7 +1991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fallowbray</t>
+          <t>Innsmere</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
@@ -2010,7 +2009,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Granleigh</t>
+          <t>Bexhollow</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
@@ -2028,7 +2027,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hesper Vale</t>
+          <t>Kettlebrook</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -2046,7 +2045,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Innsmere</t>
+          <t>Eastmoor Reach</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -2064,7 +2063,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jarrowmead</t>
+          <t>Durnsfield</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -2082,7 +2081,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kettlebrook</t>
+          <t>Jarrowmead</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lowenbrook</t>
+          <t>Fallowbray</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
